--- a/Config/Datas/map_area_effect.xlsx
+++ b/Config/Datas/map_area_effect.xlsx
@@ -135,14 +135,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -598,148 +591,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Config/Datas/map_area_effect.xlsx
+++ b/Config/Datas/map_area_effect.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -111,6 +111,9 @@
   </si>
   <si>
     <t>ground_gc_liquid</t>
+  </si>
+  <si>
+    <t>ground_milk_liquid</t>
   </si>
   <si>
     <t>ground_fire</t>
@@ -1084,10 +1087,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col min="2" max="2" width="28.25" customWidth="1"/>
+    <col min="8" max="8" width="19.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1249,33 +1253,33 @@
         <v>28</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6">
+        <v>1.5</v>
+      </c>
+      <c r="E6">
+        <v>1.5</v>
+      </c>
+      <c r="F6">
         <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>1.2</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I6">
         <v>1</v>
       </c>
       <c r="J6">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="B7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -1287,18 +1291,47 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I7">
         <v>1</v>
       </c>
       <c r="J7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0.9</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
         <v>3</v>
       </c>
     </row>

--- a/Config/Datas/map_area_effect.xlsx
+++ b/Config/Datas/map_area_effect.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="35">
   <si>
     <t>##var</t>
   </si>
@@ -113,7 +113,13 @@
     <t>ground_gc_liquid</t>
   </si>
   <si>
+    <t>b_ground_gc_liquid</t>
+  </si>
+  <si>
     <t>ground_milk_liquid</t>
+  </si>
+  <si>
+    <t>b_ground_milk_liquid</t>
   </si>
   <si>
     <t>ground_fire</t>
@@ -1239,7 +1245,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -1250,7 +1256,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="B6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1268,7 +1274,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -1279,7 +1285,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -1297,7 +1303,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -1308,7 +1314,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -1326,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I8">
         <v>1</v>

--- a/Config/Datas/map_area_effect.xlsx
+++ b/Config/Datas/map_area_effect.xlsx
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col width="28.25" customWidth="1" min="2" max="2"/>
@@ -1405,6 +1405,87 @@
         <v>1</v>
       </c>
     </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>smoke_grenade_area</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>smoke_vision_debuff</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>8</v>
+      </c>
+      <c r="K9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>flash_stun_area</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>force_stun</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>caltrop_snare_area</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>unit_stagger</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20</v>
+      </c>
+      <c r="K11" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
